--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,35 +1273,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DATA ARCHITECT</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Carroll Daniel Construction</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8b3e0cb0c3863c</t>
+          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
         </is>
       </c>
     </row>
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior IAM Integration Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior IAM Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1959975fa698f5</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1959975fa698f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b99a14ec8d003a09</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b99a14ec8d003a09</t>
+          <t>https://www.indeed.com/viewjob?jk=23be1db7b51ce1cb</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be1db7b51ce1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=041927784c1965b6</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=041927784c1965b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7494fed52583a9</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7494fed52583a9</t>
+          <t>https://www.indeed.com/viewjob?jk=074a5ef8227c514a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=074a5ef8227c514a</t>
+          <t>https://www.indeed.com/viewjob?jk=5511d29a71ff3c56</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5511d29a71ff3c56</t>
+          <t>https://www.indeed.com/viewjob?jk=8607adca5420fa46</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8607adca5420fa46</t>
+          <t>https://www.indeed.com/viewjob?jk=d756737f865a7c90</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d756737f865a7c90</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab90447c276b3c3</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab90447c276b3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4e24ab63d46d7079</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e24ab63d46d7079</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ef17383493f019</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ef17383493f019</t>
+          <t>https://www.indeed.com/viewjob?jk=081ed29e648e956d</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=081ed29e648e956d</t>
+          <t>https://www.indeed.com/viewjob?jk=34320be7fb410630</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34320be7fb410630</t>
+          <t>https://www.indeed.com/viewjob?jk=4113c6a5f4cf1088</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4113c6a5f4cf1088</t>
+          <t>https://www.indeed.com/viewjob?jk=913565719678af06</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913565719678af06</t>
+          <t>https://www.indeed.com/viewjob?jk=11a29b312afbb4f4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a29b312afbb4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=67a7ff90057076ec</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a7ff90057076ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a64ffe10514d5746</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64ffe10514d5746</t>
+          <t>https://www.indeed.com/viewjob?jk=abe591db35ba960c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe591db35ba960c</t>
+          <t>https://www.indeed.com/viewjob?jk=1160a183c15d3b85</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160a183c15d3b85</t>
+          <t>https://www.indeed.com/viewjob?jk=58248392c4bed895</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58248392c4bed895</t>
+          <t>https://www.indeed.com/viewjob?jk=b512f84c4e3c0261</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>OZ Digital</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b512f84c4e3c0261</t>
+          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Databricks Senior Data Engineer</t>
+          <t>AI/ML Data Scientist (GPSSC)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OZ Digital</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
+          <t>https://www.indeed.com/viewjob?jk=814016ce86a7c72d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Databricks Architect &amp; Developer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Des Moines, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,112 +2306,112 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Databricks, Spark</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cef02d1e7cd394</t>
+          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. ETL Databricks Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Des Moines, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Databricks, Spark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=13cef02d1e7cd394</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,102 +2456,102 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1783775bd336ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917b4fa6f284d165</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=917b4fa6f284d165</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -3308,20 +3308,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analytics (Web and Advertising Analytics)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Extractable</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MySQL, DynamoDB, ETL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286e5a815599310</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Application Developers</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Spark, Kafka, MySQL, MongoDB, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6accf9a868913e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,42 +3601,42 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Application Developers</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, LLM Platform</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>CARVANA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3807,46 +3807,46 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,102 +4101,102 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,94 +4311,94 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Member AI Features</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-4</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
+          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Azure Databricks Architect-4</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Senior Software Engineer, Member AI Features</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,15 +4686,400 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Coraopolis, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Galesburg, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>BI Reporting Developer I</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Backend Programmer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Architect</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Coresphere</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,25 +2358,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. ETL Databricks Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Des Moines, WA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Databricks, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cef02d1e7cd394</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,24 +2446,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2486,29 +2486,29 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,42 +2516,42 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917b4fa6f284d165</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,19 +3226,19 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3247,11 +3247,11 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Application Developers</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Application Developers</t>
+          <t>Software Engineer - Test Automation</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
+          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Platform</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CARVANA</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer, LLM Platform</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>CARVANA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,42 +4336,42 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Azure Databricks Architect-4</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-4</t>
+          <t>Senior Software Engineer, Member AI Features</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
+          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Member AI Features</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5045,41 +5045,6 @@
         </is>
       </c>
       <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Salesforce Solution Architect</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Coresphere</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Application Developers</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer - Test Automation</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Platform</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CARVANA</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,102 +4066,102 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
+          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,67 +4276,67 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Application Developers</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Software Engineer - Test Automation</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
+          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Software Engineer, LLM Platform</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>CARVANA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,102 +4521,102 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-4</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Member AI Features</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,277 +4731,277 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,15 +5036,680 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Engineer - Video</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Software Engineer - Video</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>AI Enablement Data Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Westbrook, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Model, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Azure Databricks Architect-4</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mahwah, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Member AI Features</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Coraopolis, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Galesburg, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>BI Reporting Developer I</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Backend Programmer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Architect</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Coresphere</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07cbf3a945c9cfd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,24 +2376,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2416,29 +2416,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,102 +3541,102 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
+          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
+          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
+          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
+          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
+          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
+          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
+          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
+          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Application Developers</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
+          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer - Test Automation</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
+          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Platform</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CARVANA</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Application Developers</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,67 +4556,67 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Software Engineer - Test Automation</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Software Engineer, LLM Platform</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>CARVANA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,29 +5001,29 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5032,46 +5032,46 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Python Backend Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>ioet</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Incline Village, NV, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,102 +5186,102 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-4</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Member AI Features</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Azure Databricks Architect-4</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer, Member AI Features</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,15 +5701,295 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Coraopolis, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Galesburg, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>BI Reporting Developer I</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ECS</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Backend Programmer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Salesforce Solution Architect</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Coresphere</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -2218,25 +2218,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI/ML Data Scientist (GPSSC)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Hadoop, Spark</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=814016ce86a7c72d</t>
+          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
+          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,24 +2376,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2416,29 +2416,29 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a424e0d64dae1bfe</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,42 +3566,42 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
+          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
+          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
+          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
+          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
+          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
+          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
+          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
+          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
+          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
+          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
+          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Software Engineer - Test Automation</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
+          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
+          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
+          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Application Developers</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Application Developers</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer - Test Automation</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Software Engineer, LLM Platform</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>CARVANA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Platform</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CARVANA</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Senior Python Backend Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ioet</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Incline Village, NV, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Python Backend Engineer</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ioet</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Incline Village, NV, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Senior AI/Python Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,67 +5221,67 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6898ec6223252736</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,25 +2288,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr. ETL Databricks Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Des Moines, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Databricks, Spark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=13cef02d1e7cd394</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,24 +2341,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2381,29 +2381,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e643c6d74eb444</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,42 +3566,42 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
+          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
+          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
+          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
+          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
+          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
+          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
+          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer - Test Automation</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
+          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>Software Engineer - Test Automation</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
+          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
+          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Application Developers</t>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Application Developers</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Roseland, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Platform</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CARVANA</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer, LLM Platform</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>CARVANA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Symmetry Lending</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Python Backend Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ioet</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Incline Village, NV, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Senior Python Backend Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>ioet</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Incline Village, NV, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior AI/Python Developer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Data Modeling, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc817ac4888de29</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Google Cloud Network Engineer</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,42 +5211,42 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,17 +5351,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6898ec6223252736</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect-4</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Mahwah, NJ, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
+          <t>https://www.indeed.com/viewjob?jk=80bd47c732eab56e</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Member AI Features</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
+          <t>https://www.indeed.com/viewjob?jk=6898ec6223252736</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Databricks Architect-4</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Mahwah, NJ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, Member AI Features</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,17 +5841,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,17 +5981,87 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Analytics Platforms</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,25 +2288,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. ETL Databricks Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Des Moines, WA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Databricks, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13cef02d1e7cd394</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,24 +2341,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2381,29 +2381,29 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Oracle, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7cee24ab74b8d09</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Scala</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e643c6d74eb444</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Software Engineer C#</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ECS, RDS, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be820bcf6998eff5</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Oracle, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21fc3ea476dd4728</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,102 +3541,102 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,67 +3751,67 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer - Test Automation</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Kafka, SQL Server, MySQL, MongoDB, NoSQL, Power BI, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=463a562e09f02043</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>Salesforce Solution Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Coresphere</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,1510 +4556,215 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
+          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Application Developers</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Roseland, NJ, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, RDS, PostgreSQL, MongoDB, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe1b2063f7fc47ae</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Scala, ETL, ELT, dbt, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8347260a96645aa2</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Platform</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CARVANA</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9642207c5b2cc59</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Analyst</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Berkeley Heights, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Scotiabank</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Guardian Bikes</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>CloudOps Specialist</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>TechnoMile</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>CloudRay Inc</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Symmetry Lending</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef450d5d3b12f873</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Python Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>ioet</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Incline Village, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>ProTalent Finders</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Software Engineer - Intermediate</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Data Integration Architect</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>University of Wisconsin-Stout</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Menomonie, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Google Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, EMR, S3, IAM, RDS, Azure, Scala, Jenkins, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9178a4cbcc55572</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Software Engineer - Video</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Software Engineer - Video</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>AI Enablement Data Engineer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>IDEXX Laboratories</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Westbrook, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Model, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Cornerstone OnDemand</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bd47c732eab56e</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6898ec6223252736</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Azure Databricks Architect-4</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Mahwah, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, NoSQL, Snowflake Schema, ETL</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=644a1f6a18efa446</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Member AI Features</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfffdbe40afac374</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Backend Programmer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Salesforce Solution Architect</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Coresphere</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Beachwood, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Coraopolis, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Galesburg, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30657c45715f4f96</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
@@ -3653,25 +3653,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Software Engineer , Backend - Dining Technology</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,52 +4056,52 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Salesforce Solution Architect</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Coresphere</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, Talend, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04680e043ccedae6</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6089961c8465fc</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>NRCCUA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Engineer C#</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Scala, ETL, ELT</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec87087b20cbd9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,52 +2971,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -3168,12 +3168,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
@@ -3618,25 +3618,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer , Backend - Dining Technology</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a55027269ae2c13</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,59 +4031,59 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5234ef7e93d3843b</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,112 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Backend Programmer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4420b6c7bc5a59dc</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,42 +2946,42 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cb5a11d2c71308d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Databricks, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f61d4f9e0de29b6</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BI Reporting Developer I</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Backend Programmer</t>
+          <t>Senior Data Architect - Analytics Platforms</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,17 +4441,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
+          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
+          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
+          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4625,41 +4625,6 @@
         </is>
       </c>
       <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The Baldwin Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbc1e170de38a542</t>
+          <t>https://www.indeed.com/viewjob?jk=1c1ca4fadb364b85</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fb7e47147703669</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ba3b099b9896af</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ddf12bf17952542</t>
+          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee6c496d5c139e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IAM Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d835fb4980e543</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>OZ Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f67d1f7e92d58f78</t>
+          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.5</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7040f1aee7737f66</t>
+          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21.5</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=860da345ddc950ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d1b2cb6836d9fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc162366041ff6c</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72da55c27901afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f1c87acc33c922</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b688f06a88c709cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platform Architect 6184507</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3305843ae9f3042d</t>
+          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>21.5</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162dea578f92102e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>21.5</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073a8ebaffd9e57c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>21.5</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eafc79be2600e030</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21.5</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fde024b3eb291739</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21.5</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1646af17e97ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53784fb2b4d41b90</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a1ba5de59cfedc</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20.1</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c1ca4fadb364b85</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-2</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20.1</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ba3b099b9896af</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>ERP DEVELOPER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Persausive technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior IAM Integration Engineer</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1959975fa698f5</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b99a14ec8d003a09</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be1db7b51ce1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=041927784c1965b6</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7494fed52583a9</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
@@ -1558,20 +1558,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=074a5ef8227c514a</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -1593,20 +1593,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5511d29a71ff3c56</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -1628,20 +1628,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8607adca5420fa46</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d756737f865a7c90</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab90447c276b3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e24ab63d46d7079</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EisnerAmper</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ef17383493f019</t>
+          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17.4</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=081ed29e648e956d</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34320be7fb410630</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4113c6a5f4cf1088</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
@@ -1908,20 +1908,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913565719678af06</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a29b312afbb4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a7ff90057076ec</t>
+          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64ffe10514d5746</t>
+          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe591db35ba960c</t>
+          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160a183c15d3b85</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58248392c4bed895</t>
+          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b512f84c4e3c0261</t>
+          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Databricks Senior Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OZ Digital</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>17.4</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
+          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
+          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>16</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
+          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>15.3</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NRCCUA</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, API Gateway, IAM, RDS, Databricks, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d638d27bd496aac</t>
+          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AI Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Python Backend Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ioet</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Incline Village, NV, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,102 +3261,102 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=80bd47c732eab56e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=6898ec6223252736</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Backend Programmer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,882 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Software Engineer - Intermediate</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>ProTalent Finders</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Integration Architect</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>University of Wisconsin-Stout</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Menomonie, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>The Cadmus Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>AI Enablement Data Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>IDEXX Laboratories</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Westbrook, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Model, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer - Video</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Software Engineer - Video</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Backend Programmer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Beachwood, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15d02502aba945ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Coraopolis, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb52e9c6f43c27d</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Galesburg, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c7ecb6b8d2b3f93</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b18883612d9ca325</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=780d004f45bf8f3f</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Data Architect - Analytics Platforms</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0945c969df98f8e0</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer (React + Node.js)-2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Baldwin Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,52 +486,52 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Databricks, Unity Catalog</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c1ca4fadb364b85</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ba3b099b9896af</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-2</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ba3b099b9896af</t>
+          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
         </is>
       </c>
     </row>
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior IAM Integration Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior IAM Integration Engineer</t>
+          <t>Databricks Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OZ Digital</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
+          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OZ Digital</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
+          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
+          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
+          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,72 +876,72 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ERP DEVELOPER</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Persausive technologies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fc1be542dcacf1</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,42 +1371,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,77 +1676,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EisnerAmper</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Power BI, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573d09f867190b28</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>CloudOps Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>TechnoMile</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>RogueSearch</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>CloudRay Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,242 +2106,242 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,54 +2561,54 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Architect</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d95a5ce61d1bd23</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,882 +2876,42 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>RogueSearch</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CloudRay Inc</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71b8c7a77228590a</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Python Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>ioet</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Incline Village, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>ProTalent Finders</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data Integration Architect</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>University of Wisconsin-Stout</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Menomonie, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Software Engineer - Intermediate</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>The Cadmus Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>AI Enablement Data Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>IDEXX Laboratories</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Westbrook, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Model, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Software Engineer - Video</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer - Video</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Cornerstone OnDemand</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bd47c732eab56e</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6898ec6223252736</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Backend Programmer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba0910a235eb75af</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Databricks Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>OZ Digital</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68c4aadfa37313dc</t>
+          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba86e480fe3755cd</t>
+          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior IAM Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b82fbb2e1ad7212</t>
+          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OZ Digital</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
+          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SR DATA SCIENTIST, SMART MFG &amp; AI</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Cleerly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12881722cc760412</t>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer, Business Intelligence</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, BigQuery, Snowflake, Oracle, PostgreSQL, MySQL, MongoDB, Tableau</t>
+          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9088b884cc79245f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Microsoft Azure Engineer / Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>Expert Technology Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1048ac2a929a355</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,129 +1791,129 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CloudOps Specialist</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TechnoMile</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0602f10e5c420065</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RogueSearch</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30c7e8de15bdeb</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mid-Senior BI / Data Engineer – Oracle HCM Analytics</t>
+          <t>Data Integration Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CloudRay Inc</t>
+          <t>University of Wisconsin-Stout</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Menomonie, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Spark, PySpark, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, Talend</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,242 +2106,242 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c341eb25b16ef9ac</t>
+          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2595,321 +2595,6 @@
         </is>
       </c>
       <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Software Engineer - Video</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Software Engineer - Video</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Microsoft Azure Engineer / Architect</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Expert Technology Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,52 +1081,52 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ECS, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc7fa4175844c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,69 +1431,69 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Developer - Power BI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Neighborhood Health Center</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tigard, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>ProTalent Finders</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
         </is>
       </c>
     </row>
@@ -2043,25 +2043,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Integration Architect</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>University of Wisconsin-Stout</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Menomonie, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb4a42fcc433ea24</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Video</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6902022dae079f0</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,112 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,25 +853,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Business Intelligence</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Spark, Scala, Snowflake, dbt, CI/CD, GitHub Actions</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f39474e07389a32</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI/ML Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,52 +1046,52 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer - Power BI</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Neighborhood Health Center</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tigard, OR, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17a304efb77ff78</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Guardian Bikes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MLOps Engineer - NO VISA SPONSORSHIP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ProTalent Finders</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d5540e90f82629</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Video</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a237a79dc97e081</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Reporting Developer I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2385,111 +2385,6 @@
         </is>
       </c>
       <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Event Hubs, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17e8e0a1dc510cf</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,52 +1011,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,69 +1361,69 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Guardian Bikes</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, BigQuery, Cloud Storage, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78011a5d6c324570</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,77 +1886,77 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>National Association of Boards of Pharmacy (NABP)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Model, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,122 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>BI Reporting Developer I</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>ECS</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>ECS, RDS, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, Dimension Tables, ETL</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe4ac8a6ea16a0a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,7 +958,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI/ML Developer</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,52 +976,52 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Splunk, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c8a3c6f4ba6dbe</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Health-E Commerce</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Halvik</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d69e074834d3c5</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,42 +1291,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,77 +1816,77 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Enablement Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>National Association of Boards of Pharmacy (NABP)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Model, CO, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Scala, Snowflake, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aa97bcb9debb40e</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,120 +2166,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
         </is>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ba3b099b9896af</t>
+          <t>https://www.indeed.com/viewjob?jk=cbc1e170de38a542</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OZ Digital</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
+          <t>https://www.indeed.com/viewjob?jk=2fb7e47147703669</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
+          <t>https://www.indeed.com/viewjob?jk=3ddf12bf17952542</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
+          <t>https://www.indeed.com/viewjob?jk=cee6c496d5c139e0</t>
         </is>
       </c>
     </row>
@@ -613,20 +613,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=47d835fb4980e543</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f67d1f7e92d58f78</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>21.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=7040f1aee7737f66</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>21.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=860da345ddc950ad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>21.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=04d1b2cb6836d9fb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>21.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc162366041ff6c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>21.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=72da55c27901afb4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>21.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f1c87acc33c922</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>21.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=b688f06a88c709cf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Back End Engineer (Node / AWS / GraphQL / Angular)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>21.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4440da75e00ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=3305843ae9f3042d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>21.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=162dea578f92102e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>21.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=073a8ebaffd9e57c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>21.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=eafc79be2600e030</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>21.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=fde024b3eb291739</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>21.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1646af17e97ebd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>21.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=53784fb2b4d41b90</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>21.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Event Hubs, GCP, BigQuery, Dataflow, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=38a1ba5de59cfedc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Full Stack Engineer (React + Node.js)-2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>20.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ba3b099b9896af</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1959975fa698f5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=b99a14ec8d003a09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=23be1db7b51ce1cb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=041927784c1965b6</t>
         </is>
       </c>
     </row>
@@ -1383,20 +1383,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7494fed52583a9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=074a5ef8227c514a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>17.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+          <t>https://www.indeed.com/viewjob?jk=5511d29a71ff3c56</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=8607adca5420fa46</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,277 +1546,277 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+          <t>https://www.indeed.com/viewjob?jk=d756737f865a7c90</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab90447c276b3c3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Galesburg, MI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+          <t>https://www.indeed.com/viewjob?jk=4e24ab63d46d7079</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ef17383493f019</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=081ed29e648e956d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+          <t>https://www.indeed.com/viewjob?jk=34320be7fb410630</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+          <t>https://www.indeed.com/viewjob?jk=4113c6a5f4cf1088</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=913565719678af06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>17.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+          <t>https://www.indeed.com/viewjob?jk=11a29b312afbb4f4</t>
         </is>
       </c>
     </row>
@@ -1838,20 +1838,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Cadmus Group, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+          <t>https://www.indeed.com/viewjob?jk=67a7ff90057076ec</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+          <t>https://www.indeed.com/viewjob?jk=a64ffe10514d5746</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Enablement Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=abe591db35ba960c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+          <t>https://www.indeed.com/viewjob?jk=1160a183c15d3b85</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
+          <t>https://www.indeed.com/viewjob?jk=58248392c4bed895</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+          <t>https://www.indeed.com/viewjob?jk=b512f84c4e3c0261</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>OZ Digital</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>17.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
         </is>
       </c>
     </row>
@@ -2118,20 +2118,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>16</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,42 +2141,2387 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
+          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Deerfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ABI Document Support Services</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Loma Linda, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Cloud Platform Architect 6184507</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Next Gen Software Solutions</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Berkeley Heights, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Crum &amp; Forster</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Checkmate</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DevOps Engineer III</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cleerly</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Data Engineering Consultant</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ippon</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NoSQL DBA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Objectways Technologies</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior, AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior, AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior, AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior, AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Power BI Architect Consultant</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>smartbridge, LLC</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sifted</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Full Stack</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ETL Developer - On-Site</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Regions Financial</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Hoover, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Product</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Art of Problem Solving Academy</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer/Analyst</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Berkeley Heights, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Scotiabank</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Python Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ioet</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Incline Village, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Coraopolis, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Galesburg, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Beachwood, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Eaton</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer - Intermediate</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>MuleSoft QA Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>The Cadmus Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AI Enablement Data Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>IDEXX Laboratories</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Westbrook, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SR SOFTWARE ENGINEER</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Blue Ash, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cornerstone OnDemand</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Dublin, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80bd47c732eab56e</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>MuleSoft Developer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6898ec6223252736</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>JPMorganChase</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Houston, TX, US USA</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D113" t="n">
         <v>10.4</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-02-28.xlsx
+++ b/results/job_matches_2026-02-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,35 +1203,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ba3b099b9896af</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1959975fa698f5</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1959975fa698f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b99a14ec8d003a09</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b99a14ec8d003a09</t>
+          <t>https://www.indeed.com/viewjob?jk=23be1db7b51ce1cb</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23be1db7b51ce1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=041927784c1965b6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=041927784c1965b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7494fed52583a9</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7494fed52583a9</t>
+          <t>https://www.indeed.com/viewjob?jk=074a5ef8227c514a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=074a5ef8227c514a</t>
+          <t>https://www.indeed.com/viewjob?jk=5511d29a71ff3c56</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5511d29a71ff3c56</t>
+          <t>https://www.indeed.com/viewjob?jk=8607adca5420fa46</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8607adca5420fa46</t>
+          <t>https://www.indeed.com/viewjob?jk=d756737f865a7c90</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d756737f865a7c90</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab90447c276b3c3</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ab90447c276b3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=4e24ab63d46d7079</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e24ab63d46d7079</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ef17383493f019</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ef17383493f019</t>
+          <t>https://www.indeed.com/viewjob?jk=081ed29e648e956d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=081ed29e648e956d</t>
+          <t>https://www.indeed.com/viewjob?jk=34320be7fb410630</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34320be7fb410630</t>
+          <t>https://www.indeed.com/viewjob?jk=4113c6a5f4cf1088</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4113c6a5f4cf1088</t>
+          <t>https://www.indeed.com/viewjob?jk=913565719678af06</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913565719678af06</t>
+          <t>https://www.indeed.com/viewjob?jk=11a29b312afbb4f4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Dover, DE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a29b312afbb4f4</t>
+          <t>https://www.indeed.com/viewjob?jk=67a7ff90057076ec</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dover, DE, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a7ff90057076ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a64ffe10514d5746</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a64ffe10514d5746</t>
+          <t>https://www.indeed.com/viewjob?jk=abe591db35ba960c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe591db35ba960c</t>
+          <t>https://www.indeed.com/viewjob?jk=1160a183c15d3b85</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1160a183c15d3b85</t>
+          <t>https://www.indeed.com/viewjob?jk=58248392c4bed895</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Wellesley, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58248392c4bed895</t>
+          <t>https://www.indeed.com/viewjob?jk=b512f84c4e3c0261</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wellesley, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Dataflow, Spark, Spark Streaming, Kafka, NoSQL</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b512f84c4e3c0261</t>
+          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Databricks Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OZ Digital</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86a35b352ed2af92</t>
+          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396e79600c7b7785</t>
+          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65fc3a984a32f89</t>
+          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ABI Document Support Services</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Loma Linda, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e25e29cf79bdd7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43abcc36eb8446d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4cf195aaa007f2e9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ABI Document Support Services</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Loma Linda, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50896f9c545c8e6b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Platform Architect 6184507</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Crum &amp; Forster</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93cf16a3466a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer (Spark, Hadoop, OzoneCH) |Berkley Heights, NJ- 5 Days Onsite | Contract W2</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Checkmate</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, MapReduce, HBase, YARN, Spark, Scala</t>
+          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a2bce135021c448</t>
+          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineering Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Crum &amp; Forster</t>
+          <t>Ippon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, RDS, Scala, Kafka</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,137 +2351,137 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e5863d850559839</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Checkmate</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=102e9f75d4db155a</t>
+          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>NoSQL DBA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cleerly</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, Scala, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e56f4ee4c4c94216</t>
+          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424f6b090b8c9279</t>
+          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineering Consultant</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ippon</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, MySQL, NoSQL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,59 +2491,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0e863463f2d399</t>
+          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NoSQL DBA</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HBase, Scala, MongoDB, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483159feaebbb175</t>
+          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, AI Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Health-E Commerce</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, Azure, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec27c4fa8782043e</t>
+          <t>https://www.indeed.com/viewjob?jk=cba73fbf347a2d2f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Power BI Architect Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>smartbridge, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1465abac94aef44</t>
+          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Sifted</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127d50b68ee25934</t>
+          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a62279dd7d6ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior, AI Platform Engineer</t>
+          <t>Desarrollador/a Python</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>PCD Systems</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82271fe81048d340</t>
+          <t>https://www.indeed.com/viewjob?jk=acc8bd8fffcdf6ca</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Power BI Architect Consultant</t>
+          <t>Cloud Platform Engineer (ML DevOps)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>smartbridge, LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f5a84578fa6353d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>ETL Developer - On-Site</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sifted</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Scala, ELT, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18bfc6e6a18ce553</t>
+          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer/Analyst</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7478241a40f20926</t>
+          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ETL Developer - On-Site</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Impala, Spark, PySpark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c192fc13269c775</t>
+          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,242 +2911,242 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991ff35a7c2f8bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b899c29e2338bfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer (ML DevOps)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Galesburg, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f5dba6447d1b44</t>
+          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226aa9de4680594d</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Solutions (MS SQL Server &amp; Oracle, AWS)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4680be027f6217fa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fed890816f98c21a</t>
+          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d2929ef2c2fdd0d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>The Cadmus Group, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12df91b6cdc7fa6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796c61e06a65c276</t>
+          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39347208d21394c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1b9627aebac5d14</t>
+          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5261cc1a75e4d83d</t>
+          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decc7b3883a9daaa</t>
+          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06028d30fc6be51b</t>
+          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,1127 +3401,42 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe64a55728ceb6d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f07af49dfee5a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8070145be149f2e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da0046da80953ecb</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38490842631d2458</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d19c1c5238e77c52</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae2fd505156bc28</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1af3ad4538a91c4a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Solutions Senior Architect - Financial Data, Compliance &amp; Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a11ef26223f8a95</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist - Product</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Art of Problem Solving Academy</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60462ec1b41e6c17</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Analyst</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Berkeley Heights, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, ETL, ELT, Power BI, Tableau, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c24add604f0e3d4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Scotiabank</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1a19fc16385452e</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Python Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>ioet</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Incline Village, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, Kafka, Oracle, DynamoDB, Docker</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bdf76bdee6d63f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Coraopolis, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a30c08c042046757</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Galesburg, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80435a84c6dcf987</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b3bbb5a3a4ff3d01</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f429cf999244a1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Beachwood, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96b26560d478e414</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Eaton</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d77c13ca89923a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32b3fe14b4fffbc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Software Engineer - Intermediate</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, SQL Server, MySQL, CI/CD, Maven, Airflow</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee15734bdb43fdbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0790b5b13b42987f</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>The Cadmus Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Hive, Spark, Scala, ETL, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c78a1ef66cf949e</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Data Engineer - AI (Spark, Databricks and Healthcare)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, Spark, Kafka, Snowflake, Oracle</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7611a3d0f3243be8</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>AI Enablement Data Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>IDEXX Laboratories</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Westbrook, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, dbt, CI/CD</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eed16d28c472ffad</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>SR SOFTWARE ENGINEER</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Blue Ash, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, Cloud Storage, Scala, Kafka, Cassandra, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3729be3511fd845</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Cornerstone OnDemand</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Spark, Scala, NoSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80bd47c732eab56e</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>MuleSoft Developer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6898ec6223252736</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=2f682083d0dc40d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=253b4229a965edaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de153392693f7c06</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70dab1aee50a9fa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72cb7fc26a2e57d</t>
         </is>
       </c>
     </row>
